--- a/ETF Regime mode/walkforward/SPY/wf_regime_SPY_1e-07_5e-04_8_5.xlsx
+++ b/ETF Regime mode/walkforward/SPY/wf_regime_SPY_1e-07_5e-04_8_5.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="91" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="93" uniqueCount="77">
   <si>
     <t>Ticker</t>
   </si>
@@ -51,6 +51,9 @@
     <t>BuyConfirmDays</t>
   </si>
   <si>
+    <t>RegimeRiskOffScale</t>
+  </si>
+  <si>
     <t>BuyHoldReturnPct</t>
   </si>
   <si>
@@ -184,6 +187,9 @@
   </si>
   <si>
     <t>SPYRegimeRiskOnPct</t>
+  </si>
+  <si>
+    <t>AverageRegimeScalePct</t>
   </si>
   <si>
     <t>BuyHoldExcessReturnPct</t>
@@ -283,7 +289,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BU10"/>
+  <dimension ref="A1:BW10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83984375" customWidth="true"/>
@@ -296,69 +302,71 @@
     <col min="8" max="8" width="6.9453125" customWidth="true"/>
     <col min="9" max="9" width="13.9453125" customWidth="true"/>
     <col min="10" max="10" width="14.20703125" customWidth="true"/>
-    <col min="11" max="11" width="15.5234375" customWidth="true"/>
-    <col min="12" max="12" width="15.3671875" customWidth="true"/>
-    <col min="13" max="13" width="16.1015625" customWidth="true"/>
-    <col min="14" max="14" width="15.5234375" customWidth="true"/>
-    <col min="15" max="15" width="20.68359375" customWidth="true"/>
-    <col min="16" max="16" width="22.3125" customWidth="true"/>
-    <col min="17" max="17" width="22.15625" customWidth="true"/>
-    <col min="18" max="18" width="22.89453125" customWidth="true"/>
-    <col min="19" max="19" width="22.3125" customWidth="true"/>
-    <col min="20" max="20" width="27.47265625" customWidth="true"/>
-    <col min="21" max="21" width="13.20703125" customWidth="true"/>
-    <col min="22" max="22" width="13.15625" customWidth="true"/>
-    <col min="23" max="23" width="13.7890625" customWidth="true"/>
-    <col min="24" max="24" width="13.20703125" customWidth="true"/>
-    <col min="25" max="25" width="18.3671875" customWidth="true"/>
-    <col min="26" max="26" width="15.41796875" customWidth="true"/>
-    <col min="27" max="27" width="15.26171875" customWidth="true"/>
-    <col min="28" max="28" width="16" customWidth="true"/>
-    <col min="29" max="29" width="15.41796875" customWidth="true"/>
-    <col min="30" max="30" width="20.578125" customWidth="true"/>
-    <col min="31" max="31" width="15.15625" customWidth="true"/>
-    <col min="32" max="32" width="15" customWidth="true"/>
-    <col min="33" max="33" width="15.734375" customWidth="true"/>
-    <col min="34" max="34" width="15.15625" customWidth="true"/>
-    <col min="35" max="35" width="20.3125" customWidth="true"/>
-    <col min="36" max="36" width="16.99609375" customWidth="true"/>
-    <col min="37" max="37" width="16.83984375" customWidth="true"/>
-    <col min="38" max="38" width="17.578125" customWidth="true"/>
-    <col min="39" max="39" width="16.99609375" customWidth="true"/>
-    <col min="40" max="40" width="22.15625" customWidth="true"/>
-    <col min="41" max="41" width="21.3671875" customWidth="true"/>
-    <col min="42" max="42" width="21.20703125" customWidth="true"/>
-    <col min="43" max="43" width="21.9453125" customWidth="true"/>
-    <col min="44" max="44" width="21.3671875" customWidth="true"/>
-    <col min="45" max="45" width="26.5234375" customWidth="true"/>
-    <col min="46" max="46" width="17.20703125" customWidth="true"/>
-    <col min="47" max="47" width="23.83984375" customWidth="true"/>
-    <col min="48" max="48" width="29" customWidth="true"/>
-    <col min="49" max="49" width="19.5234375" customWidth="true"/>
-    <col min="50" max="50" width="24.1015625" customWidth="true"/>
-    <col min="51" max="51" width="27.20703125" customWidth="true"/>
-    <col min="52" max="52" width="25.41796875" customWidth="true"/>
-    <col min="53" max="53" width="14" customWidth="true"/>
-    <col min="54" max="54" width="21.734375" customWidth="true"/>
-    <col min="55" max="55" width="17.68359375" customWidth="true"/>
-    <col min="56" max="56" width="20.578125" customWidth="true"/>
-    <col min="57" max="57" width="20.41796875" customWidth="true"/>
-    <col min="58" max="58" width="21.15625" customWidth="true"/>
-    <col min="59" max="59" width="20.578125" customWidth="true"/>
-    <col min="60" max="60" width="25.734375" customWidth="true"/>
-    <col min="61" max="61" width="29.62890625" customWidth="true"/>
-    <col min="62" max="62" width="29.47265625" customWidth="true"/>
-    <col min="63" max="63" width="30.20703125" customWidth="true"/>
-    <col min="64" max="64" width="29.62890625" customWidth="true"/>
-    <col min="65" max="65" width="34.7890625" customWidth="true"/>
-    <col min="66" max="66" width="23.99609375" customWidth="true"/>
-    <col min="67" max="67" width="23.83984375" customWidth="true"/>
-    <col min="68" max="68" width="24.578125" customWidth="true"/>
-    <col min="69" max="69" width="23.99609375" customWidth="true"/>
-    <col min="70" max="70" width="29.15625" customWidth="true"/>
-    <col min="71" max="71" width="29.15625" customWidth="true"/>
-    <col min="72" max="72" width="43.26171875" customWidth="true"/>
-    <col min="73" max="73" width="37.62890625" customWidth="true"/>
+    <col min="11" max="11" width="16.578125" customWidth="true"/>
+    <col min="12" max="12" width="15.5234375" customWidth="true"/>
+    <col min="13" max="13" width="15.3671875" customWidth="true"/>
+    <col min="14" max="14" width="16.1015625" customWidth="true"/>
+    <col min="15" max="15" width="15.5234375" customWidth="true"/>
+    <col min="16" max="16" width="20.68359375" customWidth="true"/>
+    <col min="17" max="17" width="22.3125" customWidth="true"/>
+    <col min="18" max="18" width="22.15625" customWidth="true"/>
+    <col min="19" max="19" width="22.89453125" customWidth="true"/>
+    <col min="20" max="20" width="22.3125" customWidth="true"/>
+    <col min="21" max="21" width="27.47265625" customWidth="true"/>
+    <col min="22" max="22" width="13.20703125" customWidth="true"/>
+    <col min="23" max="23" width="13.15625" customWidth="true"/>
+    <col min="24" max="24" width="13.7890625" customWidth="true"/>
+    <col min="25" max="25" width="13.20703125" customWidth="true"/>
+    <col min="26" max="26" width="18.3671875" customWidth="true"/>
+    <col min="27" max="27" width="15.41796875" customWidth="true"/>
+    <col min="28" max="28" width="15.26171875" customWidth="true"/>
+    <col min="29" max="29" width="16" customWidth="true"/>
+    <col min="30" max="30" width="15.41796875" customWidth="true"/>
+    <col min="31" max="31" width="20.578125" customWidth="true"/>
+    <col min="32" max="32" width="15.15625" customWidth="true"/>
+    <col min="33" max="33" width="15" customWidth="true"/>
+    <col min="34" max="34" width="15.734375" customWidth="true"/>
+    <col min="35" max="35" width="15.15625" customWidth="true"/>
+    <col min="36" max="36" width="20.3125" customWidth="true"/>
+    <col min="37" max="37" width="16.99609375" customWidth="true"/>
+    <col min="38" max="38" width="16.83984375" customWidth="true"/>
+    <col min="39" max="39" width="17.578125" customWidth="true"/>
+    <col min="40" max="40" width="16.99609375" customWidth="true"/>
+    <col min="41" max="41" width="22.15625" customWidth="true"/>
+    <col min="42" max="42" width="21.3671875" customWidth="true"/>
+    <col min="43" max="43" width="21.20703125" customWidth="true"/>
+    <col min="44" max="44" width="21.9453125" customWidth="true"/>
+    <col min="45" max="45" width="21.3671875" customWidth="true"/>
+    <col min="46" max="46" width="26.5234375" customWidth="true"/>
+    <col min="47" max="47" width="17.20703125" customWidth="true"/>
+    <col min="48" max="48" width="23.83984375" customWidth="true"/>
+    <col min="49" max="49" width="29" customWidth="true"/>
+    <col min="50" max="50" width="19.5234375" customWidth="true"/>
+    <col min="51" max="51" width="24.1015625" customWidth="true"/>
+    <col min="52" max="52" width="27.20703125" customWidth="true"/>
+    <col min="53" max="53" width="25.41796875" customWidth="true"/>
+    <col min="54" max="54" width="14" customWidth="true"/>
+    <col min="55" max="55" width="21.734375" customWidth="true"/>
+    <col min="56" max="56" width="17.68359375" customWidth="true"/>
+    <col min="57" max="57" width="19.89453125" customWidth="true"/>
+    <col min="58" max="58" width="20.578125" customWidth="true"/>
+    <col min="59" max="59" width="20.41796875" customWidth="true"/>
+    <col min="60" max="60" width="21.15625" customWidth="true"/>
+    <col min="61" max="61" width="20.578125" customWidth="true"/>
+    <col min="62" max="62" width="25.734375" customWidth="true"/>
+    <col min="63" max="63" width="29.62890625" customWidth="true"/>
+    <col min="64" max="64" width="29.47265625" customWidth="true"/>
+    <col min="65" max="65" width="30.20703125" customWidth="true"/>
+    <col min="66" max="66" width="29.62890625" customWidth="true"/>
+    <col min="67" max="67" width="34.7890625" customWidth="true"/>
+    <col min="68" max="68" width="23.99609375" customWidth="true"/>
+    <col min="69" max="69" width="23.83984375" customWidth="true"/>
+    <col min="70" max="70" width="24.578125" customWidth="true"/>
+    <col min="71" max="71" width="23.99609375" customWidth="true"/>
+    <col min="72" max="72" width="29.15625" customWidth="true"/>
+    <col min="73" max="73" width="29.15625" customWidth="true"/>
+    <col min="74" max="74" width="43.26171875" customWidth="true"/>
+    <col min="75" max="75" width="37.62890625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -581,6 +589,12 @@
       <c r="BU1" s="0" t="s">
         <v>74</v>
       </c>
+      <c r="BV1" s="0" t="s">
+        <v>75</v>
+      </c>
+      <c r="BW1" s="0" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -614,55 +628,55 @@
         <v>5</v>
       </c>
       <c r="K2" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="L2" s="0">
         <v>-4.5690856356264682</v>
       </c>
-      <c r="L2" s="0">
+      <c r="M2" s="0">
         <v>-5.3677709816334573</v>
       </c>
-      <c r="M2" s="0">
+      <c r="N2" s="0">
         <v>-6.9985792072600024</v>
       </c>
-      <c r="N2" s="0">
+      <c r="O2" s="0">
         <v>-5.3677709816334573</v>
       </c>
-      <c r="O2" s="0">
-        <v>-6.0382118136828478</v>
-      </c>
       <c r="P2" s="0">
-        <v>-19.351436257194486</v>
+        <v>-5.3677709816334573</v>
       </c>
       <c r="Q2" s="0">
         <v>-19.351436257194486</v>
       </c>
       <c r="R2" s="0">
+        <v>-19.351436257194486</v>
+      </c>
+      <c r="S2" s="0">
         <v>-19.359720450587503</v>
       </c>
-      <c r="S2" s="0">
+      <c r="T2" s="0">
         <v>-19.351436257194486</v>
       </c>
-      <c r="T2" s="0">
-        <v>-19.351436257194599</v>
-      </c>
       <c r="U2" s="0">
+        <v>-19.351436257194486</v>
+      </c>
+      <c r="V2" s="0">
         <v>-0.19029490039202343</v>
       </c>
-      <c r="V2" s="0">
+      <c r="W2" s="0">
         <v>-0.24047415976865014</v>
       </c>
-      <c r="W2" s="0">
+      <c r="X2" s="0">
         <v>-0.34964545072189851</v>
       </c>
-      <c r="X2" s="0">
+      <c r="Y2" s="0">
         <v>-0.24047415976865014</v>
       </c>
-      <c r="Y2" s="0">
-        <v>-0.28283735591115916</v>
-      </c>
       <c r="Z2" s="0">
-        <v>1</v>
+        <v>-0.24047415976865014</v>
       </c>
       <c r="AA2" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" s="0">
         <v>0</v>
@@ -677,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="AF2" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" s="0">
         <v>1</v>
@@ -689,25 +703,25 @@
         <v>1</v>
       </c>
       <c r="AJ2" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK2" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL2" s="0">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="0">
         <v>8</v>
       </c>
-      <c r="AM2" s="0">
-        <v>1</v>
-      </c>
       <c r="AN2" s="0">
         <v>1</v>
       </c>
       <c r="AO2" s="0">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="AP2" s="0">
-        <v>98.804780876494021</v>
+        <v>100</v>
       </c>
       <c r="AQ2" s="0">
         <v>98.804780876494021</v>
@@ -719,88 +733,94 @@
         <v>98.804780876494021</v>
       </c>
       <c r="AT2" s="0">
+        <v>98.804780876494021</v>
+      </c>
+      <c r="AU2" s="0">
         <v>98.207171314741032</v>
-      </c>
-      <c r="AU2" s="0">
-        <v>98.804780876494021</v>
       </c>
       <c r="AV2" s="0">
         <v>98.804780876494021</v>
       </c>
       <c r="AW2" s="0">
+        <v>98.804780876494021</v>
+      </c>
+      <c r="AX2" s="0">
         <v>1.6999999999999997</v>
       </c>
-      <c r="AX2" s="0">
-        <v>1</v>
-      </c>
       <c r="AY2" s="0">
+        <v>1</v>
+      </c>
+      <c r="AZ2" s="0">
         <v>8</v>
       </c>
-      <c r="AZ2" s="0">
+      <c r="BA2" s="0">
         <v>4</v>
       </c>
-      <c r="BA2" s="0">
-        <v>1</v>
-      </c>
       <c r="BB2" s="0">
+        <v>1</v>
+      </c>
+      <c r="BC2" s="0">
         <v>0.046875</v>
       </c>
-      <c r="BC2" s="0">
+      <c r="BD2" s="0">
         <v>98.804780876494021</v>
       </c>
-      <c r="BD2" s="0">
-        <v>0</v>
-      </c>
       <c r="BE2" s="0">
-        <v>-0.79868534600698871</v>
+        <v>99.402390438247011</v>
       </c>
       <c r="BF2" s="0">
-        <v>-2.4294935716335342</v>
+        <v>0</v>
       </c>
       <c r="BG2" s="0">
         <v>-0.79868534600698871</v>
       </c>
       <c r="BH2" s="0">
-        <v>-1.4691261780563791</v>
+        <v>-2.4294935716335342</v>
       </c>
       <c r="BI2" s="0">
-        <v>0</v>
+        <v>-0.79868534600698871</v>
       </c>
       <c r="BJ2" s="0">
-        <v>0</v>
+        <v>-0.79868534600698871</v>
       </c>
       <c r="BK2" s="0">
+        <v>0</v>
+      </c>
+      <c r="BL2" s="0">
+        <v>0</v>
+      </c>
+      <c r="BM2" s="0">
         <v>-0.0082841933930155598</v>
       </c>
-      <c r="BL2" s="0">
-        <v>0</v>
-      </c>
-      <c r="BM2" s="0">
-        <v>-1.1102230246251565e-13</v>
-      </c>
       <c r="BN2" s="0">
         <v>0</v>
       </c>
       <c r="BO2" s="0">
-        <v>-0.050179259376626706</v>
+        <v>0</v>
       </c>
       <c r="BP2" s="0">
-        <v>-0.15935055032987508</v>
+        <v>0</v>
       </c>
       <c r="BQ2" s="0">
         <v>-0.050179259376626706</v>
       </c>
       <c r="BR2" s="0">
-        <v>-0.09254245551913573</v>
+        <v>-0.15935055032987508</v>
       </c>
       <c r="BS2" s="0">
-        <v>-0.67044083204939042</v>
+        <v>-0.050179259376626706</v>
       </c>
       <c r="BT2" s="0">
-        <v>-1.1102230246251565e-13</v>
+        <v>-0.050179259376626706</v>
       </c>
       <c r="BU2" s="0">
-        <v>-0.042363196142509024</v>
+        <v>0</v>
+      </c>
+      <c r="BV2" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW2" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -835,10 +855,10 @@
         <v>5</v>
       </c>
       <c r="K3" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="L3" s="0">
         <v>31.221575745812657</v>
-      </c>
-      <c r="L3" s="0">
-        <v>27.598956642708174</v>
       </c>
       <c r="M3" s="0">
         <v>27.598956642708174</v>
@@ -850,7 +870,7 @@
         <v>27.598956642708174</v>
       </c>
       <c r="P3" s="0">
-        <v>-6.6194338784514422</v>
+        <v>27.598956642708174</v>
       </c>
       <c r="Q3" s="0">
         <v>-6.6194338784514422</v>
@@ -865,10 +885,10 @@
         <v>-6.6194338784514422</v>
       </c>
       <c r="U3" s="0">
+        <v>-6.6194338784514422</v>
+      </c>
+      <c r="V3" s="0">
         <v>2.235235634639432</v>
-      </c>
-      <c r="V3" s="0">
-        <v>2.1299387976520467</v>
       </c>
       <c r="W3" s="0">
         <v>2.1299387976520467</v>
@@ -880,7 +900,7 @@
         <v>2.1299387976520467</v>
       </c>
       <c r="Z3" s="0">
-        <v>1</v>
+        <v>2.1299387976520467</v>
       </c>
       <c r="AA3" s="0">
         <v>1</v>
@@ -895,7 +915,7 @@
         <v>1</v>
       </c>
       <c r="AE3" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" s="0">
         <v>0</v>
@@ -913,7 +933,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL3" s="0">
         <v>1</v>
@@ -925,10 +945,10 @@
         <v>1</v>
       </c>
       <c r="AO3" s="0">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="AP3" s="0">
-        <v>98.412698412698404</v>
+        <v>100</v>
       </c>
       <c r="AQ3" s="0">
         <v>98.412698412698404</v>
@@ -949,7 +969,7 @@
         <v>98.412698412698404</v>
       </c>
       <c r="AW3" s="0">
-        <v>1</v>
+        <v>98.412698412698404</v>
       </c>
       <c r="AX3" s="0">
         <v>1</v>
@@ -958,25 +978,25 @@
         <v>1</v>
       </c>
       <c r="AZ3" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA3" s="0">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="0">
         <v>0.375</v>
       </c>
-      <c r="BB3" s="0">
+      <c r="BC3" s="0">
         <v>0.0030241935483870967</v>
       </c>
-      <c r="BC3" s="0">
+      <c r="BD3" s="0">
         <v>98.412698412698404</v>
       </c>
-      <c r="BD3" s="0">
-        <v>0</v>
-      </c>
       <c r="BE3" s="0">
-        <v>-3.6226191031044852</v>
+        <v>99.206349206349216</v>
       </c>
       <c r="BF3" s="0">
-        <v>-3.6226191031044852</v>
+        <v>0</v>
       </c>
       <c r="BG3" s="0">
         <v>-3.6226191031044852</v>
@@ -985,10 +1005,10 @@
         <v>-3.6226191031044852</v>
       </c>
       <c r="BI3" s="0">
-        <v>0</v>
+        <v>-3.6226191031044852</v>
       </c>
       <c r="BJ3" s="0">
-        <v>0</v>
+        <v>-3.6226191031044852</v>
       </c>
       <c r="BK3" s="0">
         <v>0</v>
@@ -1003,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="BO3" s="0">
-        <v>-0.10529683698738523</v>
+        <v>0</v>
       </c>
       <c r="BP3" s="0">
-        <v>-0.10529683698738523</v>
+        <v>0</v>
       </c>
       <c r="BQ3" s="0">
         <v>-0.10529683698738523</v>
@@ -1015,12 +1035,18 @@
         <v>-0.10529683698738523</v>
       </c>
       <c r="BS3" s="0">
-        <v>0</v>
+        <v>-0.10529683698738523</v>
       </c>
       <c r="BT3" s="0">
-        <v>0</v>
+        <v>-0.10529683698738523</v>
       </c>
       <c r="BU3" s="0">
+        <v>0</v>
+      </c>
+      <c r="BV3" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW3" s="0">
         <v>0</v>
       </c>
     </row>
@@ -1056,25 +1082,25 @@
         <v>5</v>
       </c>
       <c r="K4" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="L4" s="0">
         <v>18.335809706936089</v>
       </c>
-      <c r="L4" s="0">
+      <c r="M4" s="0">
         <v>44.259680131501035</v>
       </c>
-      <c r="M4" s="0">
+      <c r="N4" s="0">
         <v>44.913651096031934</v>
       </c>
-      <c r="N4" s="0">
+      <c r="O4" s="0">
         <v>44.259680131501035</v>
       </c>
-      <c r="O4" s="0">
-        <v>42.917358681990493</v>
-      </c>
       <c r="P4" s="0">
+        <v>44.259680131501035</v>
+      </c>
+      <c r="Q4" s="0">
         <v>-33.715385820778579</v>
-      </c>
-      <c r="Q4" s="0">
-        <v>-12.430243974198675</v>
       </c>
       <c r="R4" s="0">
         <v>-12.430243974198675</v>
@@ -1083,25 +1109,25 @@
         <v>-12.430243974198675</v>
       </c>
       <c r="T4" s="0">
-        <v>-12.430243974198685</v>
+        <v>-12.430243974198675</v>
       </c>
       <c r="U4" s="0">
+        <v>-12.430243974198675</v>
+      </c>
+      <c r="V4" s="0">
         <v>0.67018718454210757</v>
       </c>
-      <c r="V4" s="0">
+      <c r="W4" s="0">
         <v>1.7876808309470249</v>
       </c>
-      <c r="W4" s="0">
+      <c r="X4" s="0">
         <v>1.8231915600487971</v>
       </c>
-      <c r="X4" s="0">
+      <c r="Y4" s="0">
         <v>1.7876808309470249</v>
       </c>
-      <c r="Y4" s="0">
-        <v>1.7457699429728986</v>
-      </c>
       <c r="Z4" s="0">
-        <v>1</v>
+        <v>1.7876808309470249</v>
       </c>
       <c r="AA4" s="0">
         <v>1</v>
@@ -1116,10 +1142,10 @@
         <v>1</v>
       </c>
       <c r="AE4" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" s="0">
         <v>1</v>
@@ -1131,25 +1157,25 @@
         <v>1</v>
       </c>
       <c r="AJ4" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK4" s="0">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="0">
         <v>2</v>
       </c>
-      <c r="AL4" s="0">
+      <c r="AM4" s="0">
         <v>4</v>
-      </c>
-      <c r="AM4" s="0">
-        <v>2</v>
       </c>
       <c r="AN4" s="0">
         <v>2</v>
       </c>
       <c r="AO4" s="0">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="AP4" s="0">
-        <v>92.490118577075094</v>
+        <v>100</v>
       </c>
       <c r="AQ4" s="0">
         <v>92.490118577075094</v>
@@ -1161,88 +1187,94 @@
         <v>92.490118577075094</v>
       </c>
       <c r="AT4" s="0">
+        <v>92.490118577075094</v>
+      </c>
+      <c r="AU4" s="0">
         <v>92.351778656126484</v>
-      </c>
-      <c r="AU4" s="0">
-        <v>92.490118577075094</v>
       </c>
       <c r="AV4" s="0">
         <v>92.490118577075094</v>
       </c>
       <c r="AW4" s="0">
-        <v>2</v>
+        <v>92.490118577075094</v>
       </c>
       <c r="AX4" s="0">
         <v>2</v>
       </c>
       <c r="AY4" s="0">
+        <v>2</v>
+      </c>
+      <c r="AZ4" s="0">
         <v>4</v>
       </c>
-      <c r="AZ4" s="0">
-        <v>0</v>
-      </c>
       <c r="BA4" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB4" s="0">
+        <v>1</v>
+      </c>
+      <c r="BC4" s="0">
         <v>0.026175213675213676</v>
       </c>
-      <c r="BC4" s="0">
+      <c r="BD4" s="0">
         <v>92.490118577075094</v>
       </c>
-      <c r="BD4" s="0">
-        <v>0</v>
-      </c>
       <c r="BE4" s="0">
-        <v>25.923870424564942</v>
+        <v>96.245059288537547</v>
       </c>
       <c r="BF4" s="0">
-        <v>26.577841389095845</v>
+        <v>0</v>
       </c>
       <c r="BG4" s="0">
         <v>25.923870424564942</v>
       </c>
       <c r="BH4" s="0">
-        <v>24.581548975054403</v>
+        <v>26.577841389095845</v>
       </c>
       <c r="BI4" s="0">
-        <v>0</v>
+        <v>25.923870424564942</v>
       </c>
       <c r="BJ4" s="0">
-        <v>21.285141846579904</v>
+        <v>25.923870424564942</v>
       </c>
       <c r="BK4" s="0">
-        <v>21.285141846579904</v>
+        <v>0</v>
       </c>
       <c r="BL4" s="0">
         <v>21.285141846579904</v>
       </c>
       <c r="BM4" s="0">
-        <v>21.28514184657989</v>
+        <v>21.285141846579904</v>
       </c>
       <c r="BN4" s="0">
-        <v>0</v>
+        <v>21.285141846579904</v>
       </c>
       <c r="BO4" s="0">
-        <v>1.1174936464049172</v>
+        <v>21.285141846579904</v>
       </c>
       <c r="BP4" s="0">
-        <v>1.1530043755066894</v>
+        <v>0</v>
       </c>
       <c r="BQ4" s="0">
         <v>1.1174936464049172</v>
       </c>
       <c r="BR4" s="0">
-        <v>1.0755827584307909</v>
+        <v>1.1530043755066894</v>
       </c>
       <c r="BS4" s="0">
-        <v>-1.3423214495105418</v>
+        <v>1.1174936464049172</v>
       </c>
       <c r="BT4" s="0">
-        <v>-1.1102230246251565e-14</v>
+        <v>1.1174936464049172</v>
       </c>
       <c r="BU4" s="0">
-        <v>-0.041910887974126343</v>
+        <v>0</v>
+      </c>
+      <c r="BV4" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW4" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1277,7 +1309,7 @@
         <v>5</v>
       </c>
       <c r="K5" s="0">
-        <v>28.732781664834683</v>
+        <v>0.5</v>
       </c>
       <c r="L5" s="0">
         <v>28.732781664834683</v>
@@ -1289,10 +1321,10 @@
         <v>28.732781664834683</v>
       </c>
       <c r="O5" s="0">
-        <v>30.50749346265933</v>
+        <v>28.732781664834683</v>
       </c>
       <c r="P5" s="0">
-        <v>-5.1143070679695146</v>
+        <v>28.732781664834683</v>
       </c>
       <c r="Q5" s="0">
         <v>-5.1143070679695146</v>
@@ -1304,10 +1336,10 @@
         <v>-5.1143070679695146</v>
       </c>
       <c r="T5" s="0">
-        <v>-5.1143070679695697</v>
+        <v>-5.1143070679695146</v>
       </c>
       <c r="U5" s="0">
-        <v>2.0107261521397488</v>
+        <v>-5.1143070679695146</v>
       </c>
       <c r="V5" s="0">
         <v>2.0107261521397488</v>
@@ -1319,13 +1351,13 @@
         <v>2.0107261521397488</v>
       </c>
       <c r="Y5" s="0">
-        <v>2.1290451750113473</v>
+        <v>2.0107261521397488</v>
       </c>
       <c r="Z5" s="0">
-        <v>1</v>
+        <v>2.0107261521397488</v>
       </c>
       <c r="AA5" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="0">
         <v>0</v>
@@ -1367,7 +1399,7 @@
         <v>0</v>
       </c>
       <c r="AO5" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AP5" s="0">
         <v>100</v>
@@ -1391,7 +1423,7 @@
         <v>100</v>
       </c>
       <c r="AW5" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AX5" s="0">
         <v>0</v>
@@ -1409,13 +1441,13 @@
         <v>0</v>
       </c>
       <c r="BC5" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BD5" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE5" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF5" s="0">
         <v>0</v>
@@ -1424,7 +1456,7 @@
         <v>0</v>
       </c>
       <c r="BH5" s="0">
-        <v>1.7747117978246463</v>
+        <v>0</v>
       </c>
       <c r="BI5" s="0">
         <v>0</v>
@@ -1439,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="BM5" s="0">
-        <v>-5.5511151231257827e-14</v>
+        <v>0</v>
       </c>
       <c r="BN5" s="0">
         <v>0</v>
@@ -1454,16 +1486,22 @@
         <v>0</v>
       </c>
       <c r="BR5" s="0">
-        <v>0.11831902287159846</v>
+        <v>0</v>
       </c>
       <c r="BS5" s="0">
-        <v>1.7747117978246463</v>
+        <v>0</v>
       </c>
       <c r="BT5" s="0">
-        <v>-5.5511151231257827e-14</v>
+        <v>0</v>
       </c>
       <c r="BU5" s="0">
-        <v>0.11831902287159846</v>
+        <v>0</v>
+      </c>
+      <c r="BV5" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW5" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -1498,55 +1536,55 @@
         <v>5</v>
       </c>
       <c r="K6" s="0">
+        <v>0.5</v>
+      </c>
+      <c r="L6" s="0">
         <v>-18.172028536815223</v>
       </c>
-      <c r="L6" s="0">
+      <c r="M6" s="0">
         <v>-15.637795904287955</v>
       </c>
-      <c r="M6" s="0">
+      <c r="N6" s="0">
         <v>-16.635757411668795</v>
       </c>
-      <c r="N6" s="0">
+      <c r="O6" s="0">
         <v>-15.637795904287955</v>
       </c>
-      <c r="O6" s="0">
-        <v>-16.125309250159013</v>
-      </c>
       <c r="P6" s="0">
+        <v>-15.637795904287955</v>
+      </c>
+      <c r="Q6" s="0">
         <v>-24.495450885579995</v>
       </c>
-      <c r="Q6" s="0">
+      <c r="R6" s="0">
         <v>-24.07360476659418</v>
       </c>
-      <c r="R6" s="0">
+      <c r="S6" s="0">
         <v>-24.497326364091109</v>
       </c>
-      <c r="S6" s="0">
+      <c r="T6" s="0">
         <v>-24.07360476659418</v>
       </c>
-      <c r="T6" s="0">
-        <v>-24.073604766594158</v>
-      </c>
       <c r="U6" s="0">
+        <v>-24.07360476659418</v>
+      </c>
+      <c r="V6" s="0">
         <v>-0.70940817269533907</v>
       </c>
-      <c r="V6" s="0">
+      <c r="W6" s="0">
         <v>-0.68843779145003703</v>
       </c>
-      <c r="W6" s="0">
+      <c r="X6" s="0">
         <v>-0.74861337666224703</v>
       </c>
-      <c r="X6" s="0">
+      <c r="Y6" s="0">
         <v>-0.68843779145003703</v>
       </c>
-      <c r="Y6" s="0">
-        <v>-0.7159526678607121</v>
-      </c>
       <c r="Z6" s="0">
-        <v>1</v>
+        <v>-0.68843779145003703</v>
       </c>
       <c r="AA6" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AB6" s="0">
         <v>3</v>
@@ -1558,10 +1596,10 @@
         <v>3</v>
       </c>
       <c r="AE6" s="0">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF6" s="0">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AG6" s="0">
         <v>3</v>
@@ -1573,25 +1611,25 @@
         <v>3</v>
       </c>
       <c r="AJ6" s="0">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK6" s="0">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="0">
         <v>6</v>
       </c>
-      <c r="AL6" s="0">
+      <c r="AM6" s="0">
         <v>12</v>
-      </c>
-      <c r="AM6" s="0">
-        <v>6</v>
       </c>
       <c r="AN6" s="0">
         <v>6</v>
       </c>
       <c r="AO6" s="0">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="AP6" s="0">
-        <v>82.470119521912352</v>
+        <v>100</v>
       </c>
       <c r="AQ6" s="0">
         <v>82.470119521912352</v>
@@ -1603,88 +1641,94 @@
         <v>82.470119521912352</v>
       </c>
       <c r="AT6" s="0">
+        <v>82.470119521912352</v>
+      </c>
+      <c r="AU6" s="0">
         <v>82.051792828685251</v>
-      </c>
-      <c r="AU6" s="0">
-        <v>82.470119521912352</v>
       </c>
       <c r="AV6" s="0">
         <v>82.470119521912352</v>
       </c>
       <c r="AW6" s="0">
-        <v>6</v>
+        <v>82.470119521912352</v>
       </c>
       <c r="AX6" s="0">
         <v>6</v>
       </c>
       <c r="AY6" s="0">
+        <v>6</v>
+      </c>
+      <c r="AZ6" s="0">
         <v>12</v>
       </c>
-      <c r="AZ6" s="0">
-        <v>0</v>
-      </c>
       <c r="BA6" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB6" s="0">
+        <v>1</v>
+      </c>
+      <c r="BC6" s="0">
         <v>0.068840579710144928</v>
       </c>
-      <c r="BC6" s="0">
+      <c r="BD6" s="0">
         <v>82.470119521912352</v>
       </c>
-      <c r="BD6" s="0">
-        <v>0</v>
-      </c>
       <c r="BE6" s="0">
-        <v>2.5342326325272668</v>
+        <v>91.235059760956176</v>
       </c>
       <c r="BF6" s="0">
-        <v>1.5362711251464267</v>
+        <v>0</v>
       </c>
       <c r="BG6" s="0">
         <v>2.5342326325272668</v>
       </c>
       <c r="BH6" s="0">
-        <v>2.0467192866562067</v>
+        <v>1.5362711251464267</v>
       </c>
       <c r="BI6" s="0">
-        <v>0</v>
+        <v>2.5342326325272668</v>
       </c>
       <c r="BJ6" s="0">
-        <v>0.42184611898581359</v>
+        <v>2.5342326325272668</v>
       </c>
       <c r="BK6" s="0">
-        <v>-0.0018754785111152472</v>
+        <v>0</v>
       </c>
       <c r="BL6" s="0">
         <v>0.42184611898581359</v>
       </c>
       <c r="BM6" s="0">
-        <v>0.42184611898583579</v>
+        <v>-0.0018754785111152472</v>
       </c>
       <c r="BN6" s="0">
-        <v>0</v>
+        <v>0.42184611898581359</v>
       </c>
       <c r="BO6" s="0">
-        <v>0.020970381245302039</v>
+        <v>0.42184611898581359</v>
       </c>
       <c r="BP6" s="0">
-        <v>-0.039205203966907964</v>
+        <v>0</v>
       </c>
       <c r="BQ6" s="0">
         <v>0.020970381245302039</v>
       </c>
       <c r="BR6" s="0">
-        <v>-0.0065444951653730321</v>
+        <v>-0.039205203966907964</v>
       </c>
       <c r="BS6" s="0">
-        <v>-0.4875133458710601</v>
+        <v>0.020970381245302039</v>
       </c>
       <c r="BT6" s="0">
-        <v>2.2204460492503131e-14</v>
+        <v>0.020970381245302039</v>
       </c>
       <c r="BU6" s="0">
-        <v>-0.027514876410675071</v>
+        <v>0</v>
+      </c>
+      <c r="BV6" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW6" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1719,7 +1763,7 @@
         <v>5</v>
       </c>
       <c r="K7" s="0">
-        <v>26.175843201130313</v>
+        <v>0.5</v>
       </c>
       <c r="L7" s="0">
         <v>26.175843201130313</v>
@@ -1731,10 +1775,10 @@
         <v>26.175843201130313</v>
       </c>
       <c r="O7" s="0">
-        <v>26.709581673468531</v>
+        <v>26.175843201130313</v>
       </c>
       <c r="P7" s="0">
-        <v>-9.9744880277077392</v>
+        <v>26.175843201130313</v>
       </c>
       <c r="Q7" s="0">
         <v>-9.9744880277077392</v>
@@ -1746,10 +1790,10 @@
         <v>-9.9744880277077392</v>
       </c>
       <c r="T7" s="0">
-        <v>-9.9744880277076948</v>
+        <v>-9.9744880277077392</v>
       </c>
       <c r="U7" s="0">
-        <v>1.8582694680421219</v>
+        <v>-9.9744880277077392</v>
       </c>
       <c r="V7" s="0">
         <v>1.8582694680421219</v>
@@ -1761,13 +1805,13 @@
         <v>1.8582694680421219</v>
       </c>
       <c r="Y7" s="0">
-        <v>1.8921947726738522</v>
+        <v>1.8582694680421219</v>
       </c>
       <c r="Z7" s="0">
-        <v>1</v>
+        <v>1.8582694680421219</v>
       </c>
       <c r="AA7" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB7" s="0">
         <v>0</v>
@@ -1809,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="AO7" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AP7" s="0">
         <v>100</v>
@@ -1833,7 +1877,7 @@
         <v>100</v>
       </c>
       <c r="AW7" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AX7" s="0">
         <v>0</v>
@@ -1845,19 +1889,19 @@
         <v>0</v>
       </c>
       <c r="BA7" s="0">
+        <v>0</v>
+      </c>
+      <c r="BB7" s="0">
         <v>0.375</v>
       </c>
-      <c r="BB7" s="0">
+      <c r="BC7" s="0">
         <v>0.0060000000000000001</v>
       </c>
-      <c r="BC7" s="0">
-        <v>100</v>
-      </c>
       <c r="BD7" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE7" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF7" s="0">
         <v>0</v>
@@ -1866,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="BH7" s="0">
-        <v>0.53373847233821881</v>
+        <v>0</v>
       </c>
       <c r="BI7" s="0">
         <v>0</v>
@@ -1881,7 +1925,7 @@
         <v>0</v>
       </c>
       <c r="BM7" s="0">
-        <v>4.4408920985006262e-14</v>
+        <v>0</v>
       </c>
       <c r="BN7" s="0">
         <v>0</v>
@@ -1896,16 +1940,22 @@
         <v>0</v>
       </c>
       <c r="BR7" s="0">
-        <v>0.033925304631730269</v>
+        <v>0</v>
       </c>
       <c r="BS7" s="0">
-        <v>0.53373847233821881</v>
+        <v>0</v>
       </c>
       <c r="BT7" s="0">
-        <v>4.4408920985006262e-14</v>
+        <v>0</v>
       </c>
       <c r="BU7" s="0">
-        <v>0.033925304631730269</v>
+        <v>0</v>
+      </c>
+      <c r="BV7" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW7" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1940,7 +1990,7 @@
         <v>5</v>
       </c>
       <c r="K8" s="0">
-        <v>24.886296603431646</v>
+        <v>0.5</v>
       </c>
       <c r="L8" s="0">
         <v>24.886296603431646</v>
@@ -1952,10 +2002,10 @@
         <v>24.886296603431646</v>
       </c>
       <c r="O8" s="0">
-        <v>25.589017895139389</v>
+        <v>24.886296603431646</v>
       </c>
       <c r="P8" s="0">
-        <v>-8.4055178970657511</v>
+        <v>24.886296603431646</v>
       </c>
       <c r="Q8" s="0">
         <v>-8.4055178970657511</v>
@@ -1967,10 +2017,10 @@
         <v>-8.4055178970657511</v>
       </c>
       <c r="T8" s="0">
-        <v>-8.4055178970657281</v>
+        <v>-8.4055178970657511</v>
       </c>
       <c r="U8" s="0">
-        <v>1.8316019878865235</v>
+        <v>-8.4055178970657511</v>
       </c>
       <c r="V8" s="0">
         <v>1.8316019878865235</v>
@@ -1982,13 +2032,13 @@
         <v>1.8316019878865235</v>
       </c>
       <c r="Y8" s="0">
-        <v>1.8786076218927625</v>
+        <v>1.8316019878865235</v>
       </c>
       <c r="Z8" s="0">
-        <v>1</v>
+        <v>1.8316019878865235</v>
       </c>
       <c r="AA8" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" s="0">
         <v>0</v>
@@ -2030,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="AO8" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AP8" s="0">
         <v>100</v>
@@ -2054,7 +2104,7 @@
         <v>100</v>
       </c>
       <c r="AW8" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AX8" s="0">
         <v>0</v>
@@ -2066,19 +2116,19 @@
         <v>0</v>
       </c>
       <c r="BA8" s="0">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="0">
         <v>0.375</v>
       </c>
-      <c r="BB8" s="0">
+      <c r="BC8" s="0">
         <v>0.0064484126984126981</v>
       </c>
-      <c r="BC8" s="0">
-        <v>100</v>
-      </c>
       <c r="BD8" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE8" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF8" s="0">
         <v>0</v>
@@ -2087,7 +2137,7 @@
         <v>0</v>
       </c>
       <c r="BH8" s="0">
-        <v>0.70272129170774189</v>
+        <v>0</v>
       </c>
       <c r="BI8" s="0">
         <v>0</v>
@@ -2102,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="BM8" s="0">
-        <v>2.2204460492503131e-14</v>
+        <v>0</v>
       </c>
       <c r="BN8" s="0">
         <v>0</v>
@@ -2117,16 +2167,22 @@
         <v>0</v>
       </c>
       <c r="BR8" s="0">
-        <v>0.047005634006239028</v>
+        <v>0</v>
       </c>
       <c r="BS8" s="0">
-        <v>0.70272129170774189</v>
+        <v>0</v>
       </c>
       <c r="BT8" s="0">
-        <v>2.2204460492503131e-14</v>
+        <v>0</v>
       </c>
       <c r="BU8" s="0">
-        <v>0.047005634006239028</v>
+        <v>0</v>
+      </c>
+      <c r="BV8" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW8" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2161,55 +2217,55 @@
         <v>5</v>
       </c>
       <c r="K9" s="0">
-        <v>16.702577170503385</v>
+        <v>0.5</v>
       </c>
       <c r="L9" s="0">
         <v>16.702577170503385</v>
       </c>
       <c r="M9" s="0">
+        <v>16.702577170503385</v>
+      </c>
+      <c r="N9" s="0">
         <v>16.351076253481335</v>
       </c>
-      <c r="N9" s="0">
+      <c r="O9" s="0">
         <v>16.702577170503385</v>
       </c>
-      <c r="O9" s="0">
-        <v>16.990085556891831</v>
-      </c>
       <c r="P9" s="0">
-        <v>-18.755277437767138</v>
+        <v>16.702577170503385</v>
       </c>
       <c r="Q9" s="0">
         <v>-18.755277437767138</v>
       </c>
       <c r="R9" s="0">
+        <v>-18.755277437767138</v>
+      </c>
+      <c r="S9" s="0">
         <v>-19.112493346658866</v>
       </c>
-      <c r="S9" s="0">
+      <c r="T9" s="0">
         <v>-18.755277437767138</v>
       </c>
-      <c r="T9" s="0">
-        <v>-18.75527743776717</v>
-      </c>
       <c r="U9" s="0">
-        <v>0.89546472171375724</v>
+        <v>-18.755277437767138</v>
       </c>
       <c r="V9" s="0">
         <v>0.89546472171375724</v>
       </c>
       <c r="W9" s="0">
+        <v>0.89546472171375724</v>
+      </c>
+      <c r="X9" s="0">
         <v>0.88284182635205932</v>
       </c>
-      <c r="X9" s="0">
+      <c r="Y9" s="0">
         <v>0.89546472171375724</v>
       </c>
-      <c r="Y9" s="0">
-        <v>0.90829675756495964</v>
-      </c>
       <c r="Z9" s="0">
-        <v>1</v>
+        <v>0.89546472171375724</v>
       </c>
       <c r="AA9" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" s="0">
         <v>0</v>
@@ -2242,16 +2298,16 @@
         <v>0</v>
       </c>
       <c r="AL9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="0">
         <v>5</v>
       </c>
-      <c r="AM9" s="0">
-        <v>0</v>
-      </c>
       <c r="AN9" s="0">
         <v>0</v>
       </c>
       <c r="AO9" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AP9" s="0">
         <v>100</v>
@@ -2266,50 +2322,50 @@
         <v>100</v>
       </c>
       <c r="AT9" s="0">
+        <v>100</v>
+      </c>
+      <c r="AU9" s="0">
         <v>99.539999999999992</v>
       </c>
-      <c r="AU9" s="0">
-        <v>100</v>
-      </c>
       <c r="AV9" s="0">
         <v>100</v>
       </c>
       <c r="AW9" s="0">
+        <v>100</v>
+      </c>
+      <c r="AX9" s="0">
         <v>0.69999999999999996</v>
       </c>
-      <c r="AX9" s="0">
-        <v>0</v>
-      </c>
       <c r="AY9" s="0">
+        <v>0</v>
+      </c>
+      <c r="AZ9" s="0">
         <v>5</v>
       </c>
-      <c r="AZ9" s="0">
+      <c r="BA9" s="0">
         <v>4</v>
       </c>
-      <c r="BA9" s="0">
+      <c r="BB9" s="0">
         <v>0.875</v>
       </c>
-      <c r="BB9" s="0">
+      <c r="BC9" s="0">
         <v>0.025000000000000001</v>
       </c>
-      <c r="BC9" s="0">
-        <v>100</v>
-      </c>
       <c r="BD9" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE9" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BG9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BH9" s="0">
         <v>-0.35150091702205177</v>
       </c>
-      <c r="BG9" s="0">
-        <v>0</v>
-      </c>
-      <c r="BH9" s="0">
-        <v>0.28750838638844645</v>
-      </c>
       <c r="BI9" s="0">
         <v>0</v>
       </c>
@@ -2317,14 +2373,14 @@
         <v>0</v>
       </c>
       <c r="BK9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BL9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BM9" s="0">
         <v>-0.35721590889172816</v>
       </c>
-      <c r="BL9" s="0">
-        <v>0</v>
-      </c>
-      <c r="BM9" s="0">
-        <v>-3.3306690738754696e-14</v>
-      </c>
       <c r="BN9" s="0">
         <v>0</v>
       </c>
@@ -2332,22 +2388,28 @@
         <v>0</v>
       </c>
       <c r="BP9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BQ9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BR9" s="0">
         <v>-0.012622895361697917</v>
       </c>
-      <c r="BQ9" s="0">
-        <v>0</v>
-      </c>
-      <c r="BR9" s="0">
-        <v>0.012832035851202406</v>
-      </c>
       <c r="BS9" s="0">
-        <v>0.28750838638844645</v>
+        <v>0</v>
       </c>
       <c r="BT9" s="0">
-        <v>-3.3306690738754696e-14</v>
+        <v>0</v>
       </c>
       <c r="BU9" s="0">
-        <v>0.012832035851202406</v>
+        <v>0</v>
+      </c>
+      <c r="BV9" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW9" s="0">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2382,7 +2444,7 @@
         <v>5</v>
       </c>
       <c r="K10" s="0">
-        <v>10.932367433130064</v>
+        <v>0.5</v>
       </c>
       <c r="L10" s="0">
         <v>10.932367433130064</v>
@@ -2394,10 +2456,10 @@
         <v>10.932367433130064</v>
       </c>
       <c r="O10" s="0">
-        <v>10.729393855116465</v>
+        <v>10.932367433130064</v>
       </c>
       <c r="P10" s="0">
-        <v>-9.1331291607355318</v>
+        <v>10.932367433130064</v>
       </c>
       <c r="Q10" s="0">
         <v>-9.1331291607355318</v>
@@ -2409,10 +2471,10 @@
         <v>-9.1331291607355318</v>
       </c>
       <c r="T10" s="0">
-        <v>-9.1331291607356313</v>
+        <v>-9.1331291607355318</v>
       </c>
       <c r="U10" s="0">
-        <v>1.968059254099956</v>
+        <v>-9.1331291607355318</v>
       </c>
       <c r="V10" s="0">
         <v>1.968059254099956</v>
@@ -2424,13 +2486,13 @@
         <v>1.968059254099956</v>
       </c>
       <c r="Y10" s="0">
-        <v>1.9344210013091538</v>
+        <v>1.968059254099956</v>
       </c>
       <c r="Z10" s="0">
-        <v>1</v>
+        <v>1.968059254099956</v>
       </c>
       <c r="AA10" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" s="0">
         <v>0</v>
@@ -2472,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="AO10" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AP10" s="0">
         <v>100</v>
@@ -2496,7 +2558,7 @@
         <v>100</v>
       </c>
       <c r="AW10" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AX10" s="0">
         <v>0</v>
@@ -2514,13 +2576,13 @@
         <v>0</v>
       </c>
       <c r="BC10" s="0">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BD10" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE10" s="0">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF10" s="0">
         <v>0</v>
@@ -2529,7 +2591,7 @@
         <v>0</v>
       </c>
       <c r="BH10" s="0">
-        <v>-0.20297357801359883</v>
+        <v>0</v>
       </c>
       <c r="BI10" s="0">
         <v>0</v>
@@ -2544,7 +2606,7 @@
         <v>0</v>
       </c>
       <c r="BM10" s="0">
-        <v>-9.9920072216264089e-14</v>
+        <v>0</v>
       </c>
       <c r="BN10" s="0">
         <v>0</v>
@@ -2559,16 +2621,22 @@
         <v>0</v>
       </c>
       <c r="BR10" s="0">
-        <v>-0.033638252790802126</v>
+        <v>0</v>
       </c>
       <c r="BS10" s="0">
-        <v>-0.20297357801359883</v>
+        <v>0</v>
       </c>
       <c r="BT10" s="0">
-        <v>-9.9920072216264089e-14</v>
+        <v>0</v>
       </c>
       <c r="BU10" s="0">
-        <v>-0.033638252790802126</v>
+        <v>0</v>
+      </c>
+      <c r="BV10" s="0">
+        <v>0</v>
+      </c>
+      <c r="BW10" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
